--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>8.855</t>
-  </si>
-  <si>
-    <t>(6.081)</t>
-  </si>
-  <si>
-    <t>16.275</t>
-  </si>
-  <si>
-    <t>(1.904)</t>
-  </si>
-  <si>
-    <t>81.803</t>
-  </si>
-  <si>
-    <t>(20.572)</t>
-  </si>
-  <si>
-    <t>106.679</t>
-  </si>
-  <si>
-    <t>(31.987)</t>
-  </si>
-  <si>
-    <t>2.886</t>
-  </si>
-  <si>
-    <t>(0.336)</t>
-  </si>
-  <si>
-    <t>20.440</t>
-  </si>
-  <si>
-    <t>(2.476)</t>
-  </si>
-  <si>
-    <t>6.207</t>
-  </si>
-  <si>
-    <t>(1.799)</t>
-  </si>
-  <si>
-    <t>6.927</t>
-  </si>
-  <si>
-    <t>(6.098)</t>
-  </si>
-  <si>
-    <t>125.827</t>
-  </si>
-  <si>
-    <t>(43.349)</t>
-  </si>
-  <si>
-    <t>91.539</t>
-  </si>
-  <si>
-    <t>(22.719)</t>
+    <t>2.776</t>
+  </si>
+  <si>
+    <t>(0.278)</t>
+  </si>
+  <si>
+    <t>16.816</t>
+  </si>
+  <si>
+    <t>(1.966)</t>
+  </si>
+  <si>
+    <t>59.647</t>
+  </si>
+  <si>
+    <t>(9.955)</t>
+  </si>
+  <si>
+    <t>70.868</t>
+  </si>
+  <si>
+    <t>(10.562)</t>
+  </si>
+  <si>
+    <t>3.018</t>
+  </si>
+  <si>
+    <t>(0.344)</t>
+  </si>
+  <si>
+    <t>21.379</t>
+  </si>
+  <si>
+    <t>(2.545)</t>
+  </si>
+  <si>
+    <t>4.592</t>
+  </si>
+  <si>
+    <t>(0.627)</t>
+  </si>
+  <si>
+    <t>0.835</t>
+  </si>
+  <si>
+    <t>(0.186)</t>
+  </si>
+  <si>
+    <t>80.350</t>
+  </si>
+  <si>
+    <t>(11.028)</t>
+  </si>
+  <si>
+    <t>63.747</t>
+  </si>
+  <si>
+    <t>(10.950)</t>
   </si>
   <si>
     <t>23</t>
@@ -198,7 +198,7 @@
     <t>(38.620)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-5.937</t>
-  </si>
-  <si>
-    <t>-1.753</t>
-  </si>
-  <si>
-    <t>73.207</t>
-  </si>
-  <si>
-    <t>60.208</t>
-  </si>
-  <si>
-    <t>-0.259</t>
-  </si>
-  <si>
-    <t>-4.440</t>
-  </si>
-  <si>
-    <t>-0.834</t>
-  </si>
-  <si>
-    <t>-5.969</t>
-  </si>
-  <si>
-    <t>57.309</t>
-  </si>
-  <si>
-    <t>60.400</t>
+    <t>0.142</t>
+  </si>
+  <si>
+    <t>-2.294</t>
+  </si>
+  <si>
+    <t>95.363***</t>
+  </si>
+  <si>
+    <t>96.019***</t>
+  </si>
+  <si>
+    <t>-0.392</t>
+  </si>
+  <si>
+    <t>-5.379</t>
+  </si>
+  <si>
+    <t>0.781</t>
+  </si>
+  <si>
+    <t>0.124</t>
+  </si>
+  <si>
+    <t>102.785***</t>
+  </si>
+  <si>
+    <t>88.193***</t>
   </si>
 </sst>
 </file>
